--- a/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
+++ b/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -1098,28 +1098,6 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>rel_spread_phi_0_45_105=3.648971557918331e-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>V0b_metric_consistency_production_grids</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>same criterion as V0 (&lt;=5e-3 linear-field metric consistency) on the grids that carry absolute-stress claims (R48, M, R192, T144); T48 (96x48) is informational</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>errors={'R48': {'chi1': '2.93e-03', 'chi2': '3.58e-03'}, 'M': {'chi1': '1.18e-03', 'chi2': '1.48e-03'}, 'R192': {'chi1': '1.04e-03', 'chi2': '1.26e-03'}, 'T144': {'chi1': '7.74e-04', 'chi2': '9.75e-04'}, 'T48': {'chi1': '4.18e-03', 'chi2': '5.03e-03'}}; worst_production_grids=0.003575961642985348</t>
         </is>
       </c>
     </row>

--- a/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
+++ b/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -713,24 +713,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>96x48 interior error &lt;5e-3 (handoff criterion), 2nd order expected</t>
+          <t>observed order &gt;= 1.9 on both refinement steps for chi = 1, 2 AND interior error &lt; 5e-3 at the production grid 192x96 (re-specified 2026-10-03; the inherited 96x48 absolute threshold is reported, not asserted)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>chi1_errs_48_96_192=[0.01668623219132792, 0.004177783115160594, 0.0010446010651126159]; chi2_errs_48_96_192=[0.019586849836125353, 0.005027908399043213, 0.001261040978100425]</t>
+          <t>chi1_errs_48_96_192=[0.01668623219132792, 0.004177783115160594, 0.0010446010651126159]; chi2_errs_48_96_192=[0.019586849836125353, 0.005027908399043213, 0.001261040978100425]; chi1_orders=[1.998, 2.0]; chi2_orders=[1.962, 1.995]; value_at_96x48_chi2=0.005027908399043213; threshold_at_96x48_chi2=0.005; exceedance_at_96x48_chi2_pct=0.5581679808642548</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V1_stencil_dispersion</t>
+          <t>V0b_metric_consistency_convergence_order</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -740,19 +740,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>|err|&lt;2% at kh=0.4 (handoff criterion)</t>
+          <t>second-order convergence of the linear-field metric error (48x24 -&gt; 96x48 -&gt; 192x96), both chi; the order check computed in V0 is asserted here as its own case</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>d2_symbol_err_kh0p4=-0.013262425036063563</t>
+          <t>orders_chi1=[1.998, 2.0]; orders_chi2=[1.962, 1.995]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V3_rotation_covariance_all_grid_aligned_phi_FIXED</t>
+          <t>V1_stencil_dispersion</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -762,19 +762,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>&lt;=1e-8 for theta, u (each normalised by its own max) and wall hoop stress, at complex s, phi=15..165 deg step 15 (exact lattice rotations of the 48-point grid)</t>
+          <t>|err|&lt;2% at kh=0.4 (handoff criterion)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>max_rel_err=6.452700984660496e-14; max_theta=5.10702591327572e-15; max_u=6.452700984660496e-14; max_wall_hoop=2.1714745065335717e-14; per_phi_worst={15: '4.4e-14', 30: '6.0e-14', 45: '3.2e-14', 60: '4.0e-14', 75: '3.6e-14', 90: '6.3e-14', 105: '5.5e-14', 120: '5.0e-14', 135: '4.7e-14', 150: '4.0e-14', 165: '6.5e-14'}</t>
+          <t>d2_symbol_err_kh0p4=-0.013262425036063563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V3p_test_power_shipped_rotation</t>
+          <t>V3_rotation_covariance_all_grid_aligned_phi_FIXED</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>the corrected test must detect the shipped bug at phi=45 (hoop &gt;1e-4) while 90 deg stays blind (&lt;1e-8)</t>
+          <t>&lt;=1e-8 for theta, u (each normalised by its own max) and wall hoop stress, at complex s, phi=15..165 deg step 15 (exact lattice rotations of the 48-point grid)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>shipped_phi45_hoop=0.002999690909305527; shipped_phi45_u=0.002629776401479041; shipped_phi45_theta=6.001452041356557e-07; shipped_phi90_worst=6.268428613852337e-14</t>
+          <t>max_rel_err=6.452700984660496e-14; max_theta=5.10702591327572e-15; max_u=6.452700984660496e-14; max_wall_hoop=2.1714745065335717e-14; per_phi_worst={15: '4.4e-14', 30: '6.0e-14', 45: '3.2e-14', 60: '4.0e-14', 75: '3.6e-14', 90: '6.3e-14', 105: '5.5e-14', 120: '5.0e-14', 135: '4.7e-14', 150: '4.0e-14', 165: '6.5e-14'}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4_uncoupled_null_beta0</t>
+          <t>V3p_test_power_shipped_rotation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -806,19 +806,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>beta=0 -&gt; u,sigma = 0 (&lt;1e-6 Pa) at complex s</t>
+          <t>the corrected test must detect the shipped bug at phi=45 (hoop &gt;1e-4) while 90 deg stays blind (&lt;1e-8)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>max_abs_hoop_Pa=0.0; backward_err=5.974403560745729e-17</t>
+          <t>shipped_phi45_hoop=0.002999690909305527; shipped_phi45_u=0.002629776401479041; shipped_phi45_theta=6.001452041356557e-07; shipped_phi90_worst=6.268428613852337e-14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V5_tau_to_zero</t>
+          <t>V4_uncoupled_null_beta0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -828,19 +828,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CV(tau=1e-6 t_th) vs Fourier at complex s &lt;=1e-4</t>
+          <t>beta=0 -&gt; u,sigma = 0 (&lt;1e-6 Pa) at complex s</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rel_diff=4.2008930602807683e-07</t>
+          <t>max_abs_hoop_Pa=0.0; backward_err=5.974403560745729e-17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V12_conjugate_symmetry</t>
+          <t>V5_tau_to_zero</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -850,19 +850,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>H(conj s) = conj H(s) for the real system (needed by the one-sided Bromwich sum) &lt;=1e-10</t>
+          <t>CV(tau=1e-6 t_th) vs Fourier at complex s &lt;=1e-4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rel_err=1.698314660101103e-15</t>
+          <t>rel_diff=4.2008930602807683e-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_steady_log_law</t>
+          <t>V12_conjugate_symmetry</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -872,19 +872,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>&lt;=0.01 at 96x48 (handoff criterion); ratio of successive errors ~4 expected</t>
+          <t>H(conj s) = conj H(s) for the real system (needed by the one-sided Bromwich sum) &lt;=1e-10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>max_abs_err_48_96_192=[7.27999180387684e-05, 1.5365055767158076e-05, 3.6164004739713818e-06]</t>
+          <t>rel_err=1.698314660101103e-15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V7_static_uniform_theta_annulus</t>
+          <t>V6_steady_log_law</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -894,19 +894,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>&lt;=1.5% at 96x48 vs closed form (handoff criterion)</t>
+          <t>&lt;=0.01 at 96x48 (handoff criterion); ratio of successive errors ~4 expected</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rel_err_48_96_192=[0.016880767949530154, 0.004239529801282995, 0.0010591865724793384]; sigma_exact=-3179904.953001158</t>
+          <t>max_abs_err_48_96_192=[7.27999180387684e-05, 1.5365055767158076e-05, 3.6164004739713818e-06]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V8_steady_thermal_gradient_load</t>
+          <t>V7_static_uniform_theta_annulus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>steady log-profile thermal-gradient elasticity (clamped R=80a) vs closed form: |err(192x96)|&lt;0.5%, order&gt;1.5 (NEW: gradient-load path was absent from handoff V0-V7)</t>
+          <t>&lt;=1.5% at 96x48 vs closed form (handoff criterion)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rel_err_48_96_192_384=['+0.0063', '+0.0016', '+0.0004', '+0.0008']; observed_order_48_to_96=1.9675283417378677; sigma_exact=-1234746.0535908495</t>
+          <t>rel_err_48_96_192=[0.016880767949530154, 0.004239529801282995, 0.0010591865724793384]; sigma_exact=-3179904.953001158</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V9a_weighted_spectral_error_vs_1D</t>
+          <t>V8_steady_thermal_gradient_load</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -938,19 +938,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>isotropic circle, inertia+coupling ON, Fourier/CV5/CV20/MCV3-20: pulse-weighted spectral error at 192x96 &lt;1%, order&gt;1.5</t>
+          <t>steady log-profile thermal-gradient elasticity (clamped R=80a) vs closed form: |err(192x96)|&lt;0.5%, order&gt;1.5 (NEW: gradient-load path was absent from handoff V0-V7)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>weighted_errs={'FOURIER0': ['1.29e-02', '3.12e-03', '7.62e-04'], 'CV5': ['1.34e-02', '3.24e-03', '7.93e-04'], 'CV20': ['1.46e-02', '3.54e-03', '8.68e-04'], 'MCV320': ['1.46e-02', '3.55e-03', '8.71e-04']}; worst_192=0.0008712698489962431; min_order_48_96=2.040793659162131</t>
+          <t>rel_err_48_96_192_384=['+0.0063', '+0.0016', '+0.0004', '+0.0008']; observed_order_48_to_96=1.9675283417378677; sigma_exact=-1234746.0535908495</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V9d_time_domain_peak_and_series_vs_1D</t>
+          <t>V9a_weighted_spectral_error_vs_1D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -960,19 +960,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wall hoop series (t&lt;=6) and peak, 2-D + Bromwich vs 1-D spectral + Bromwich: |peak err(192x96)|&lt;1%, series err&lt;1.5%, order&gt;1.5</t>
+          <t>isotropic circle, inertia+coupling ON, Fourier/CV5/CV20/MCV3-20: pulse-weighted spectral error at 192x96 &lt;1%, order&gt;1.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>peak_errs={'FOURIER0': ['+0.0121', '+0.0029', '+0.0007'], 'CV5': ['+0.0121', '+0.0029', '+0.0007'], 'CV20': ['+0.0132', '+0.0030', '+0.0007'], 'MCV320': ['+0.0135', '+0.0031', '+0.0008']}; series_errs={'FOURIER0': ['0.0127', '0.0030', '0.0007'], 'CV5': ['0.0131', '0.0031', '0.0008'], 'CV20': ['0.0150', '0.0035', '0.0009'], 'MCV320': ['0.0150', '0.0036', '0.0009']}; worst_peak_192=0.0007554460804142712; worst_series_192=0.0008635894262719382; min_order_peak_48_96=2.074617052416121</t>
+          <t>weighted_errs={'FOURIER0': ['1.29e-02', '3.12e-03', '7.62e-04'], 'CV5': ['1.34e-02', '3.24e-03', '7.93e-04'], 'CV20': ['1.46e-02', '3.54e-03', '8.68e-04'], 'MCV320': ['1.46e-02', '3.55e-03', '8.71e-04']}; worst_192=0.0008712698489962431; min_order_48_96=2.040793659162131</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V9e_thermal_memory_deviation_D_accuracy</t>
+          <t>V9d_time_domain_peak_and_series_vs_1D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -982,19 +982,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D=max_t|sig_CV-sig_F|/max|sig_F| (t&lt;=6), 2-D vs 1-D reference: |rel err(192x96)|&lt;=20% (D is a small difference of two nearly equal series)</t>
+          <t>wall hoop series (t&lt;=6) and peak, 2-D + Bromwich vs 1-D spectral + Bromwich: |peak err(192x96)|&lt;1%, series err&lt;1.5%, order&gt;1.5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>detail={'CV5': {'D_1d': '3.2504e-03', 'D_2d': ['3.5857e-03', '3.3345e-03', '3.2722e-03'], 'rel_err': ['+0.103', '+0.026', '+0.007']}, 'CV20': {'D_1d': '8.9931e-03', 'D_2d': ['1.0967e-02', '9.4575e-03', '9.1100e-03'], 'rel_err': ['+0.219', '+0.052', '+0.013']}}; worst_rel_err_192=0.012998607775645632</t>
+          <t>peak_errs={'FOURIER0': ['+0.0121', '+0.0029', '+0.0007'], 'CV5': ['+0.0121', '+0.0029', '+0.0007'], 'CV20': ['+0.0132', '+0.0030', '+0.0007'], 'MCV320': ['+0.0135', '+0.0031', '+0.0008']}; series_errs={'FOURIER0': ['0.0127', '0.0030', '0.0007'], 'CV5': ['0.0131', '0.0031', '0.0008'], 'CV20': ['0.0150', '0.0035', '0.0009'], 'MCV320': ['0.0150', '0.0036', '0.0009']}; worst_peak_192=0.0007554460804142712; worst_series_192=0.0008635894262719382; min_order_peak_48_96=2.074617052416121</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V9b_dynamic_a50nm_vs_1D_time_domain</t>
+          <t>V9e_thermal_memory_deviation_D_accuracy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1004,19 +1004,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>a=50 nm, CV, 96x48, inertia+coupling ON: |peak err|&lt;3% (grid error expected ~1%)</t>
+          <t>D=max_t|sig_CV-sig_F|/max|sig_F| (t&lt;=6), 2-D vs 1-D reference: |rel err(192x96)|&lt;=20% (D is a small difference of two nearly equal series)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>peak_rel_err_96x48=0.0027435482505742204</t>
+          <t>detail={'CV5': {'D_1d': '3.2504e-03', 'D_2d': ['3.5857e-03', '3.3345e-03', '3.2722e-03'], 'rel_err': ['+0.103', '+0.026', '+0.007']}, 'CV20': {'D_1d': '8.9931e-03', 'D_2d': ['1.0967e-02', '9.4575e-03', '9.1100e-03'], 'rel_err': ['+0.219', '+0.052', '+0.013']}}; worst_rel_err_192=0.012998607775645632</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V9c_inertia_off_switch</t>
+          <t>V9b_dynamic_a50nm_vs_1D_time_domain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1026,19 +1026,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>inertia_scale=0 reproduces the 1-D quasi-static (inertia=False) reference peak to grid accuracy (&lt;3%)</t>
+          <t>a=50 nm, CV, 96x48, inertia+coupling ON: |peak err|&lt;3% (grid error expected ~1%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>peak_rel_err_96x48=0.002856533823756005</t>
+          <t>peak_rel_err_96x48=0.0027435482505742204</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V11_single_pulse_isotropic_circle_vs_time_domain</t>
+          <t>V9c_inertia_off_switch</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1048,54 +1048,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2-D mapped FD + Bromwich (inertia off, uncoupled, isotropic circle) vs independent time-domain reference: |peak err(192x96)|&lt;0.5%, order&gt;1.5</t>
+          <t>inertia_scale=0 reproduces the 1-D quasi-static (inertia=False) reference peak to grid accuracy (&lt;3%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>peak_rel_err_48_96_192=['+0.0116', '+0.0027', '+0.0007']; series_max_err_192=0.0007092278288747796; order_48_96=2.0766318319713055; order_96_192=2.0451058001284252; reference_peak_Pa_per_K=985689.4485743708</t>
+          <t>peak_rel_err_96x48=0.002856533823756005</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V3c_nonaligned_37deg_EXPLORATORY</t>
+          <t>V11_single_pulse_isotropic_circle_vs_time_domain</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>phi=37 deg is not a lattice rotation of the grid: invariance holds only to discretisation order; exploratory, no pass/fail</t>
+          <t>2-D mapped FD + Bromwich (inertia off, uncoupled, isotropic circle) vs independent time-domain reference: |peak err(192x96)|&lt;0.5%, order&gt;1.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>rel_diff={'48x24': 0.00015450198561745435, '96x48': 4.031557781056748e-06}</t>
+          <t>peak_rel_err_48_96_192=['+0.0116', '+0.0027', '+0.0007']; series_max_err_192=0.0007092278288747796; order_48_96=2.0766318319713055; order_96_192=2.0451058001284252; reference_peak_Pa_per_K=985689.4485743708</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>V3c_nonaligned_37deg_EXPLORATORY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>phi=37 deg is not a lattice rotation of the grid: invariance holds only to discretisation order; exploratory, no pass/fail</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>rel_diff={'48x24': 0.00015450198561745435, '96x48': 4.031557781056748e-06}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>V3d_peak_stress_invariance_T1_quantity</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>peak |hoop| of the anisotropic circle identical for grid-aligned phi (pre-registered T1: &lt;=1e-8), single-pulse pipeline, 48x24</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>rel_spread_phi_0_45_105=3.648971557918331e-15</t>
         </is>
@@ -3265,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9235,7 +9257,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>D_iso_circle_T48</t>
+          <t>D_iso_circle_M</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9262,23 +9284,23 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I115" t="n">
         <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>-980589.8744878817</v>
+        <v>-981309.3819665584</v>
       </c>
       <c r="K115" t="n">
-        <v>-980589.8744878817</v>
+        <v>-981309.3819665581</v>
       </c>
       <c r="L115" t="n">
         <v>2.48</v>
       </c>
       <c r="M115" t="n">
-        <v>6.200310366647481e-25</v>
+        <v>5.038866383600916e-25</v>
       </c>
       <c r="N115" t="n">
         <v>6.337471067996692e-09</v>
@@ -9287,7 +9309,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>D_iso_ellipse_M</t>
+          <t>D_iso_circle_T48</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9304,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -9314,23 +9336,23 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>96x96</t>
+          <t>96x48</t>
         </is>
       </c>
       <c r="I116" t="n">
         <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>-1500999.737590091</v>
+        <v>-980589.8744878817</v>
       </c>
       <c r="K116" t="n">
-        <v>-1500999.737572934</v>
+        <v>-980589.8744878817</v>
       </c>
       <c r="L116" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="M116" t="n">
-        <v>7.170041277649553e-25</v>
+        <v>6.200310366647481e-25</v>
       </c>
       <c r="N116" t="n">
         <v>6.337471067996692e-09</v>
@@ -9339,7 +9361,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>D_iso_ellipse_R192</t>
+          <t>D_iso_ellipse_M</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9366,23 +9388,23 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>192x96</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I117" t="n">
         <v>5</v>
       </c>
       <c r="J117" t="n">
-        <v>-1497301.581118743</v>
+        <v>-1500999.737590091</v>
       </c>
       <c r="K117" t="n">
-        <v>-1497301.581108526</v>
+        <v>-1500999.737572934</v>
       </c>
       <c r="L117" t="n">
         <v>2.55</v>
       </c>
       <c r="M117" t="n">
-        <v>1.370754290987581e-24</v>
+        <v>7.170041277649553e-25</v>
       </c>
       <c r="N117" t="n">
         <v>6.337471067996692e-09</v>
@@ -9391,7 +9413,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>D_iso_ellipse_R48</t>
+          <t>D_iso_ellipse_R192</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9418,23 +9440,23 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>48x96</t>
+          <t>192x96</t>
         </is>
       </c>
       <c r="I118" t="n">
         <v>5</v>
       </c>
       <c r="J118" t="n">
-        <v>-1509477.600634676</v>
+        <v>-1497301.581118743</v>
       </c>
       <c r="K118" t="n">
-        <v>-1509477.600691514</v>
+        <v>-1497301.581108526</v>
       </c>
       <c r="L118" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="M118" t="n">
-        <v>3.730382350845049e-25</v>
+        <v>1.370754290987581e-24</v>
       </c>
       <c r="N118" t="n">
         <v>6.337471067996692e-09</v>
@@ -9443,12 +9465,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>E1_alpha_cheng298_phi000</t>
+          <t>D_iso_ellipse_R48</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9470,23 +9492,23 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>48x96</t>
         </is>
       </c>
       <c r="I119" t="n">
         <v>5</v>
       </c>
       <c r="J119" t="n">
-        <v>-71983.07098370501</v>
+        <v>-1509477.600634676</v>
       </c>
       <c r="K119" t="n">
-        <v>-71786.88204442665</v>
+        <v>-1509477.600691514</v>
       </c>
       <c r="L119" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="M119" t="n">
-        <v>1.167982290651808e-23</v>
+        <v>3.730382350845049e-25</v>
       </c>
       <c r="N119" t="n">
         <v>6.337471067996692e-09</v>
@@ -9495,7 +9517,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>E1_alpha_cheng298_phi030</t>
+          <t>E1_alpha_cheng298_phi000</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9515,7 +9537,7 @@
         <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>10</v>
@@ -9529,16 +9551,16 @@
         <v>5</v>
       </c>
       <c r="J120" t="n">
-        <v>-78564.58628420703</v>
+        <v>-71983.07098370501</v>
       </c>
       <c r="K120" t="n">
-        <v>-78489.10654236711</v>
+        <v>-71786.88204442665</v>
       </c>
       <c r="L120" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="M120" t="n">
-        <v>8.72704684258709e-24</v>
+        <v>1.167982290651808e-23</v>
       </c>
       <c r="N120" t="n">
         <v>6.337471067996692e-09</v>
@@ -9547,12 +9569,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>E1_alpha_cheng298_phi060</t>
+          <t>E1_alpha_cheng298_phi000_M</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9567,30 +9589,30 @@
         <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>10</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I121" t="n">
         <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>-72107.03466501719</v>
+        <v>-72943.28554488087</v>
       </c>
       <c r="K121" t="n">
-        <v>-71519.73849796185</v>
+        <v>-72848.13525114262</v>
       </c>
       <c r="L121" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="M121" t="n">
-        <v>9.065527232636716e-24</v>
+        <v>1.309974911618031e-23</v>
       </c>
       <c r="N121" t="n">
         <v>6.337471067996692e-09</v>
@@ -9599,7 +9621,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>E1_alpha_cheng298_phi090</t>
+          <t>E1_alpha_cheng298_phi030</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9619,7 +9641,7 @@
         <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G122" t="n">
         <v>10</v>
@@ -9633,16 +9655,16 @@
         <v>5</v>
       </c>
       <c r="J122" t="n">
-        <v>-60048.28446171838</v>
+        <v>-78564.58628420703</v>
       </c>
       <c r="K122" t="n">
-        <v>-59954.64056006714</v>
+        <v>-78489.10654236711</v>
       </c>
       <c r="L122" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="M122" t="n">
-        <v>9.664824241412034e-24</v>
+        <v>8.72704684258709e-24</v>
       </c>
       <c r="N122" t="n">
         <v>6.337471067996692e-09</v>
@@ -9651,12 +9673,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>E1_alpha_cheng298_phi120</t>
+          <t>E1_alpha_cheng298_phi030_M</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9671,30 +9693,30 @@
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G123" t="n">
         <v>10</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>5</v>
       </c>
       <c r="J123" t="n">
-        <v>-77428.54529144388</v>
+        <v>-79631.18217352369</v>
       </c>
       <c r="K123" t="n">
-        <v>-77262.66116169</v>
+        <v>-79506.25333169969</v>
       </c>
       <c r="L123" t="n">
         <v>2.54</v>
       </c>
       <c r="M123" t="n">
-        <v>1.088031549474067e-23</v>
+        <v>1.138266584549232e-23</v>
       </c>
       <c r="N123" t="n">
         <v>6.337471067996692e-09</v>
@@ -9703,7 +9725,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>E1_alpha_cheng298_phi150</t>
+          <t>E1_alpha_cheng298_phi060</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9723,7 +9745,7 @@
         <v>2</v>
       </c>
       <c r="F124" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G124" t="n">
         <v>10</v>
@@ -9737,16 +9759,16 @@
         <v>5</v>
       </c>
       <c r="J124" t="n">
-        <v>-82091.99334955408</v>
+        <v>-72107.03466501719</v>
       </c>
       <c r="K124" t="n">
-        <v>-81478.64695208755</v>
+        <v>-71519.73849796185</v>
       </c>
       <c r="L124" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M124" t="n">
-        <v>9.203416629965348e-24</v>
+        <v>9.065527232636716e-24</v>
       </c>
       <c r="N124" t="n">
         <v>6.337471067996692e-09</v>
@@ -9755,12 +9777,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>E2_alpha_iso_phi000</t>
+          <t>E1_alpha_cheng298_phi060_M</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9775,30 +9797,30 @@
         <v>2</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G125" t="n">
         <v>10</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>5</v>
       </c>
       <c r="J125" t="n">
-        <v>-1058709.049313132</v>
+        <v>-72786.27069605948</v>
       </c>
       <c r="K125" t="n">
-        <v>-1058636.927463265</v>
+        <v>-72321.73957922928</v>
       </c>
       <c r="L125" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="M125" t="n">
-        <v>6.560530564429625e-25</v>
+        <v>8.839905495138631e-24</v>
       </c>
       <c r="N125" t="n">
         <v>6.337471067996692e-09</v>
@@ -9807,7 +9829,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>E2_alpha_iso_phi030</t>
+          <t>E1_alpha_cheng298_phi090</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9827,7 +9849,7 @@
         <v>2</v>
       </c>
       <c r="F126" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G126" t="n">
         <v>10</v>
@@ -9841,16 +9863,16 @@
         <v>5</v>
       </c>
       <c r="J126" t="n">
-        <v>-1224595.27660713</v>
+        <v>-60048.28446171838</v>
       </c>
       <c r="K126" t="n">
-        <v>-1200429.873050736</v>
+        <v>-59954.64056006714</v>
       </c>
       <c r="L126" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="M126" t="n">
-        <v>6.225439878571737e-25</v>
+        <v>9.664824241412034e-24</v>
       </c>
       <c r="N126" t="n">
         <v>6.337471067996692e-09</v>
@@ -9859,12 +9881,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>E2_alpha_iso_phi060</t>
+          <t>E1_alpha_cheng298_phi090_M</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9879,30 +9901,30 @@
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G127" t="n">
         <v>10</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I127" t="n">
         <v>5</v>
       </c>
       <c r="J127" t="n">
-        <v>-1206174.213134666</v>
+        <v>-60305.63786454877</v>
       </c>
       <c r="K127" t="n">
-        <v>-1205268.421507397</v>
+        <v>-60163.2020063216</v>
       </c>
       <c r="L127" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="M127" t="n">
-        <v>6.413928691979463e-25</v>
+        <v>1.222129598981227e-23</v>
       </c>
       <c r="N127" t="n">
         <v>6.337471067996692e-09</v>
@@ -9911,7 +9933,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>E2_alpha_iso_phi090</t>
+          <t>E1_alpha_cheng298_phi120</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9931,7 +9953,7 @@
         <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G128" t="n">
         <v>10</v>
@@ -9945,16 +9967,16 @@
         <v>5</v>
       </c>
       <c r="J128" t="n">
-        <v>-1082991.013729332</v>
+        <v>-77428.54529144388</v>
       </c>
       <c r="K128" t="n">
-        <v>-1079355.931943485</v>
+        <v>-77262.66116169</v>
       </c>
       <c r="L128" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="M128" t="n">
-        <v>6.528767565354546e-25</v>
+        <v>1.088031549474067e-23</v>
       </c>
       <c r="N128" t="n">
         <v>6.337471067996692e-09</v>
@@ -9963,12 +9985,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>E2_alpha_iso_phi120</t>
+          <t>E1_alpha_cheng298_phi120_M</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9990,23 +10012,23 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I129" t="n">
         <v>5</v>
       </c>
       <c r="J129" t="n">
-        <v>-1307547.489090703</v>
+        <v>-78346.90243940064</v>
       </c>
       <c r="K129" t="n">
-        <v>-1302813.915365322</v>
+        <v>-78238.11977070759</v>
       </c>
       <c r="L129" t="n">
         <v>2.54</v>
       </c>
       <c r="M129" t="n">
-        <v>6.494779195116172e-25</v>
+        <v>1.033355628191147e-23</v>
       </c>
       <c r="N129" t="n">
         <v>6.337471067996692e-09</v>
@@ -10015,7 +10037,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>E2_alpha_iso_phi150</t>
+          <t>E1_alpha_cheng298_phi150</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10049,16 +10071,16 @@
         <v>5</v>
       </c>
       <c r="J130" t="n">
-        <v>-1303855.555355795</v>
+        <v>-82091.99334955408</v>
       </c>
       <c r="K130" t="n">
-        <v>-1278398.558475176</v>
+        <v>-81478.64695208755</v>
       </c>
       <c r="L130" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="M130" t="n">
-        <v>6.274965534756927e-25</v>
+        <v>9.203416629965348e-24</v>
       </c>
       <c r="N130" t="n">
         <v>6.337471067996692e-09</v>
@@ -10067,12 +10089,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>E3_K_iso_phi000</t>
+          <t>E1_alpha_cheng298_phi150_M</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10087,30 +10109,30 @@
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G131" t="n">
         <v>10</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I131" t="n">
         <v>5</v>
       </c>
       <c r="J131" t="n">
-        <v>-1113039.266539694</v>
+        <v>-83388.96523236579</v>
       </c>
       <c r="K131" t="n">
-        <v>-1106147.914013555</v>
+        <v>-82878.58013196412</v>
       </c>
       <c r="L131" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="M131" t="n">
-        <v>6.669981947140855e-25</v>
+        <v>1.036273682545611e-23</v>
       </c>
       <c r="N131" t="n">
         <v>6.337471067996692e-09</v>
@@ -10119,7 +10141,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>E3_K_iso_phi030</t>
+          <t>E2_alpha_iso_phi000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10139,7 +10161,7 @@
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>10</v>
@@ -10153,16 +10175,16 @@
         <v>5</v>
       </c>
       <c r="J132" t="n">
-        <v>-1269829.428042927</v>
+        <v>-1058709.049313132</v>
       </c>
       <c r="K132" t="n">
-        <v>-1263501.136386128</v>
+        <v>-1058636.927463265</v>
       </c>
       <c r="L132" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="M132" t="n">
-        <v>6.251381397590533e-25</v>
+        <v>6.560530564429625e-25</v>
       </c>
       <c r="N132" t="n">
         <v>6.337471067996692e-09</v>
@@ -10171,12 +10193,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>E3_K_iso_phi060</t>
+          <t>E2_alpha_iso_phi000_M</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10191,30 +10213,30 @@
         <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>10</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I133" t="n">
         <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>-1199952.639045625</v>
+        <v>-1070357.933870043</v>
       </c>
       <c r="K133" t="n">
-        <v>-1195203.525471876</v>
+        <v>-1070079.888156835</v>
       </c>
       <c r="L133" t="n">
         <v>2.53</v>
       </c>
       <c r="M133" t="n">
-        <v>6.863455479460313e-25</v>
+        <v>6.465237660015981e-25</v>
       </c>
       <c r="N133" t="n">
         <v>6.337471067996692e-09</v>
@@ -10223,7 +10245,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>E3_K_iso_phi090</t>
+          <t>E2_alpha_iso_phi030</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10243,7 +10265,7 @@
         <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G134" t="n">
         <v>10</v>
@@ -10257,16 +10279,16 @@
         <v>5</v>
       </c>
       <c r="J134" t="n">
-        <v>-953760.2269122457</v>
+        <v>-1224595.27660713</v>
       </c>
       <c r="K134" t="n">
-        <v>-945619.2390858274</v>
+        <v>-1200429.873050736</v>
       </c>
       <c r="L134" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="M134" t="n">
-        <v>7.029093404898221e-25</v>
+        <v>6.225439878571737e-25</v>
       </c>
       <c r="N134" t="n">
         <v>6.337471067996692e-09</v>
@@ -10275,12 +10297,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>E3_K_iso_phi120</t>
+          <t>E2_alpha_iso_phi030_M</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10295,30 +10317,30 @@
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G135" t="n">
         <v>10</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I135" t="n">
         <v>5</v>
       </c>
       <c r="J135" t="n">
-        <v>-1193697.300852474</v>
+        <v>-1242110.719861495</v>
       </c>
       <c r="K135" t="n">
-        <v>-1193459.215217655</v>
+        <v>-1240572.24972783</v>
       </c>
       <c r="L135" t="n">
         <v>2.53</v>
       </c>
       <c r="M135" t="n">
-        <v>5.859123426554041e-25</v>
+        <v>6.580956950767184e-25</v>
       </c>
       <c r="N135" t="n">
         <v>6.337471067996692e-09</v>
@@ -10327,7 +10349,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>E3_K_iso_phi150</t>
+          <t>E2_alpha_iso_phi060</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10347,7 +10369,7 @@
         <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G136" t="n">
         <v>10</v>
@@ -10361,16 +10383,16 @@
         <v>5</v>
       </c>
       <c r="J136" t="n">
-        <v>-1237540.035901078</v>
+        <v>-1206174.213134666</v>
       </c>
       <c r="K136" t="n">
-        <v>-1223592.496826736</v>
+        <v>-1205268.421507397</v>
       </c>
       <c r="L136" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="M136" t="n">
-        <v>6.042783546161819e-25</v>
+        <v>6.413928691979463e-25</v>
       </c>
       <c r="N136" t="n">
         <v>6.337471067996692e-09</v>
@@ -10379,12 +10401,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>E4_C_iso_phi000</t>
+          <t>E2_alpha_iso_phi060_M</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10399,30 +10421,30 @@
         <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G137" t="n">
         <v>10</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I137" t="n">
         <v>5</v>
       </c>
       <c r="J137" t="n">
-        <v>-1772212.98602467</v>
+        <v>-1217839.230304825</v>
       </c>
       <c r="K137" t="n">
-        <v>-1771053.714103361</v>
+        <v>-1217113.295690076</v>
       </c>
       <c r="L137" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M137" t="n">
-        <v>6.003505437316807e-25</v>
+        <v>6.462516481359963e-25</v>
       </c>
       <c r="N137" t="n">
         <v>6.337471067996692e-09</v>
@@ -10431,7 +10453,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>E4_C_iso_phi030</t>
+          <t>E2_alpha_iso_phi090</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10451,7 +10473,7 @@
         <v>2</v>
       </c>
       <c r="F138" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G138" t="n">
         <v>10</v>
@@ -10465,16 +10487,16 @@
         <v>5</v>
       </c>
       <c r="J138" t="n">
-        <v>-1622688.092076764</v>
+        <v>-1082991.013729332</v>
       </c>
       <c r="K138" t="n">
-        <v>-1622691.213221814</v>
+        <v>-1079355.931943485</v>
       </c>
       <c r="L138" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="M138" t="n">
-        <v>5.281949039258323e-25</v>
+        <v>6.528767565354546e-25</v>
       </c>
       <c r="N138" t="n">
         <v>6.337471067996692e-09</v>
@@ -10483,12 +10505,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>E4_C_iso_phi060</t>
+          <t>E2_alpha_iso_phi090_M</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10503,30 +10525,30 @@
         <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G139" t="n">
         <v>10</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I139" t="n">
         <v>5</v>
       </c>
       <c r="J139" t="n">
-        <v>-1316500.751373346</v>
+        <v>-1089045.115949462</v>
       </c>
       <c r="K139" t="n">
-        <v>-1314329.902686277</v>
+        <v>-1086311.427544859</v>
       </c>
       <c r="L139" t="n">
         <v>2.52</v>
       </c>
       <c r="M139" t="n">
-        <v>6.843998803942505e-25</v>
+        <v>7.827326475710452e-25</v>
       </c>
       <c r="N139" t="n">
         <v>6.337471067996692e-09</v>
@@ -10535,7 +10557,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>E4_C_iso_phi090</t>
+          <t>E2_alpha_iso_phi120</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10555,7 +10577,7 @@
         <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G140" t="n">
         <v>10</v>
@@ -10569,16 +10591,16 @@
         <v>5</v>
       </c>
       <c r="J140" t="n">
-        <v>-1094324.547429828</v>
+        <v>-1307547.489090703</v>
       </c>
       <c r="K140" t="n">
-        <v>-1093999.463060109</v>
+        <v>-1302813.915365322</v>
       </c>
       <c r="L140" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="M140" t="n">
-        <v>5.853529974728048e-25</v>
+        <v>6.494779195116172e-25</v>
       </c>
       <c r="N140" t="n">
         <v>6.337471067996692e-09</v>
@@ -10587,12 +10609,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>E4_C_iso_phi120</t>
+          <t>E2_alpha_iso_phi120_M</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10614,23 +10636,23 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I141" t="n">
         <v>5</v>
       </c>
       <c r="J141" t="n">
-        <v>-1420589.926419724</v>
+        <v>-1323676.062384653</v>
       </c>
       <c r="K141" t="n">
-        <v>-1412705.179068522</v>
+        <v>-1318590.602336188</v>
       </c>
       <c r="L141" t="n">
         <v>2.54</v>
       </c>
       <c r="M141" t="n">
-        <v>6.130673009551566e-25</v>
+        <v>7.329689946146662e-25</v>
       </c>
       <c r="N141" t="n">
         <v>6.337471067996692e-09</v>
@@ -10639,7 +10661,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>E4_C_iso_phi150</t>
+          <t>E2_alpha_iso_phi150</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10673,16 +10695,16 @@
         <v>5</v>
       </c>
       <c r="J142" t="n">
-        <v>-1695321.956901297</v>
+        <v>-1303855.555355795</v>
       </c>
       <c r="K142" t="n">
-        <v>-1690325.721810431</v>
+        <v>-1278398.558475176</v>
       </c>
       <c r="L142" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="M142" t="n">
-        <v>5.942732638021689e-25</v>
+        <v>6.274965534756927e-25</v>
       </c>
       <c r="N142" t="n">
         <v>6.337471067996692e-09</v>
@@ -10691,12 +10713,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>F_tw0.3_circ</t>
+          <t>E2_alpha_iso_phi150_M</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10708,47 +10730,47 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G143" t="n">
         <v>10</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I143" t="n">
         <v>5</v>
       </c>
       <c r="J143" t="n">
-        <v>-899040.3511199263</v>
+        <v>-1324547.041558965</v>
       </c>
       <c r="K143" t="n">
-        <v>-899040.2689875197</v>
+        <v>-1323781.03423409</v>
       </c>
       <c r="L143" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="M143" t="n">
-        <v>7.001362487343579e-25</v>
+        <v>8.317906458757356e-25</v>
       </c>
       <c r="N143" t="n">
-        <v>7.267588090636986e-09</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>F_tw0.3_ell_phi090</t>
+          <t>E3_K_iso_phi000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10763,7 +10785,7 @@
         <v>2</v>
       </c>
       <c r="F144" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>10</v>
@@ -10777,30 +10799,30 @@
         <v>5</v>
       </c>
       <c r="J144" t="n">
-        <v>-977936.3031397222</v>
+        <v>-1113039.266539694</v>
       </c>
       <c r="K144" t="n">
-        <v>-977761.2990852288</v>
+        <v>-1106147.914013555</v>
       </c>
       <c r="L144" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="M144" t="n">
-        <v>8.567387374472107e-25</v>
+        <v>6.669981947140855e-25</v>
       </c>
       <c r="N144" t="n">
-        <v>7.267588090636986e-09</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>F_tw0.3_ell_phi150</t>
+          <t>E3_K_iso_phi000_M</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10815,44 +10837,44 @@
         <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>10</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I145" t="n">
         <v>5</v>
       </c>
       <c r="J145" t="n">
-        <v>-1255159.36671212</v>
+        <v>-1125623.060261802</v>
       </c>
       <c r="K145" t="n">
-        <v>-1242762.324795061</v>
+        <v>-1124863.232522883</v>
       </c>
       <c r="L145" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="M145" t="n">
-        <v>7.753581633560335e-25</v>
+        <v>6.101990794255907e-25</v>
       </c>
       <c r="N145" t="n">
-        <v>7.267588090636986e-09</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>F_tw0.6_circ</t>
+          <t>E3_K_iso_phi030</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10864,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G146" t="n">
         <v>10</v>
@@ -10881,30 +10903,30 @@
         <v>5</v>
       </c>
       <c r="J146" t="n">
-        <v>-856983.2352498674</v>
+        <v>-1269829.428042927</v>
       </c>
       <c r="K146" t="n">
-        <v>-856952.543009626</v>
+        <v>-1263501.136386128</v>
       </c>
       <c r="L146" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="M146" t="n">
-        <v>7.001362487343579e-25</v>
+        <v>6.251381397590533e-25</v>
       </c>
       <c r="N146" t="n">
-        <v>1.501920806817458e-08</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>F_tw0.6_ell_phi090</t>
+          <t>E3_K_iso_phi030_M</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10919,44 +10941,44 @@
         <v>2</v>
       </c>
       <c r="F147" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G147" t="n">
         <v>10</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>5</v>
       </c>
       <c r="J147" t="n">
-        <v>-948791.5296712716</v>
+        <v>-1288462.92650167</v>
       </c>
       <c r="K147" t="n">
-        <v>-948027.5587036546</v>
+        <v>-1280271.82702922</v>
       </c>
       <c r="L147" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="M147" t="n">
-        <v>8.567387374472107e-25</v>
+        <v>7.647107894096698e-25</v>
       </c>
       <c r="N147" t="n">
-        <v>1.501920806817458e-08</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>F_tw0.6_ell_phi150</t>
+          <t>E3_K_iso_phi060</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10971,7 +10993,7 @@
         <v>2</v>
       </c>
       <c r="F148" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G148" t="n">
         <v>10</v>
@@ -10985,30 +11007,30 @@
         <v>5</v>
       </c>
       <c r="J148" t="n">
-        <v>-1253536.4244813</v>
+        <v>-1199952.639045625</v>
       </c>
       <c r="K148" t="n">
-        <v>-1241195.863727053</v>
+        <v>-1195203.525471876</v>
       </c>
       <c r="L148" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="M148" t="n">
-        <v>7.753581633560335e-25</v>
+        <v>6.863455479460313e-25</v>
       </c>
       <c r="N148" t="n">
-        <v>1.501920806817458e-08</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>F_tw2.4_circ</t>
+          <t>E3_K_iso_phi060_M</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11020,47 +11042,47 @@
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G149" t="n">
         <v>10</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>96x96</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>5</v>
       </c>
       <c r="J149" t="n">
-        <v>-857929.4406721654</v>
+        <v>-1212722.699998106</v>
       </c>
       <c r="K149" t="n">
-        <v>-857712.0050774449</v>
+        <v>-1208673.664790181</v>
       </c>
       <c r="L149" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="M149" t="n">
-        <v>7.001362487343579e-25</v>
+        <v>7.476622437686611e-25</v>
       </c>
       <c r="N149" t="n">
-        <v>0.3196191972977383</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>F_tw2.4_ell_phi090</t>
+          <t>E3_K_iso_phi090</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11089,30 +11111,30 @@
         <v>5</v>
       </c>
       <c r="J150" t="n">
-        <v>-988606.6846172039</v>
+        <v>-953760.2269122457</v>
       </c>
       <c r="K150" t="n">
-        <v>-983550.602187245</v>
+        <v>-945619.2390858274</v>
       </c>
       <c r="L150" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M150" t="n">
-        <v>8.567387374472107e-25</v>
+        <v>7.029093404898221e-25</v>
       </c>
       <c r="N150" t="n">
-        <v>0.3196191972977383</v>
+        <v>6.337471067996692e-09</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>F_tw2.4_ell_phi150</t>
+          <t>E3_K_iso_phi090_M</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -11127,32 +11149,1332 @@
         <v>2</v>
       </c>
       <c r="F151" t="n">
+        <v>90</v>
+      </c>
+      <c r="G151" t="n">
+        <v>10</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>5</v>
+      </c>
+      <c r="J151" t="n">
+        <v>-958279.8373893192</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-958278.4821347881</v>
+      </c>
+      <c r="L151" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M151" t="n">
+        <v>6.298386661636113e-25</v>
+      </c>
+      <c r="N151" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>E3_K_iso_phi120</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>120</v>
+      </c>
+      <c r="G152" t="n">
+        <v>10</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>5</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-1193697.300852474</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-1193459.215217655</v>
+      </c>
+      <c r="L152" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M152" t="n">
+        <v>5.859123426554041e-25</v>
+      </c>
+      <c r="N152" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>E3_K_iso_phi120_M</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>120</v>
+      </c>
+      <c r="G153" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>5</v>
+      </c>
+      <c r="J153" t="n">
+        <v>-1207149.715586962</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-1207149.395953439</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M153" t="n">
+        <v>6.366671391964691e-25</v>
+      </c>
+      <c r="N153" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>E3_K_iso_phi150</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
         <v>150</v>
       </c>
-      <c r="G151" t="n">
-        <v>10</v>
-      </c>
-      <c r="H151" t="inlineStr">
+      <c r="G154" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" t="inlineStr">
         <is>
           <t>96x48</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>5</v>
-      </c>
-      <c r="J151" t="n">
+      <c r="I154" t="n">
+        <v>5</v>
+      </c>
+      <c r="J154" t="n">
+        <v>-1237540.035901078</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-1223592.496826736</v>
+      </c>
+      <c r="L154" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M154" t="n">
+        <v>6.042783546161819e-25</v>
+      </c>
+      <c r="N154" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>E3_K_iso_phi150_M</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>150</v>
+      </c>
+      <c r="G155" t="n">
+        <v>10</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>-1255521.742109912</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-1251509.175571938</v>
+      </c>
+      <c r="L155" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M155" t="n">
+        <v>5.889788194459709e-25</v>
+      </c>
+      <c r="N155" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi000</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>10</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>5</v>
+      </c>
+      <c r="J156" t="n">
+        <v>-1772212.98602467</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-1771053.714103361</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M156" t="n">
+        <v>6.003505437316807e-25</v>
+      </c>
+      <c r="N156" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi000_M</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>10</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>5</v>
+      </c>
+      <c r="J157" t="n">
+        <v>-1787990.847821061</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-1786766.251230331</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M157" t="n">
+        <v>7.50504762170729e-25</v>
+      </c>
+      <c r="N157" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi030</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" t="n">
+        <v>30</v>
+      </c>
+      <c r="G158" t="n">
+        <v>10</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>5</v>
+      </c>
+      <c r="J158" t="n">
+        <v>-1622688.092076764</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-1622691.213221814</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M158" t="n">
+        <v>5.281949039258323e-25</v>
+      </c>
+      <c r="N158" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi030_M</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2</v>
+      </c>
+      <c r="F159" t="n">
+        <v>30</v>
+      </c>
+      <c r="G159" t="n">
+        <v>10</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>-1634732.590551824</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-1634607.549381406</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M159" t="n">
+        <v>6.598195228367349e-25</v>
+      </c>
+      <c r="N159" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi060</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" t="n">
+        <v>60</v>
+      </c>
+      <c r="G160" t="n">
+        <v>10</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>-1316500.751373346</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-1314329.902686277</v>
+      </c>
+      <c r="L160" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M160" t="n">
+        <v>6.843998803942505e-25</v>
+      </c>
+      <c r="N160" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi060_M</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" t="n">
+        <v>60</v>
+      </c>
+      <c r="G161" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>5</v>
+      </c>
+      <c r="J161" t="n">
+        <v>-1323837.134229319</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-1322807.158638081</v>
+      </c>
+      <c r="L161" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M161" t="n">
+        <v>6.0262361703117e-25</v>
+      </c>
+      <c r="N161" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi090</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>90</v>
+      </c>
+      <c r="G162" t="n">
+        <v>10</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>5</v>
+      </c>
+      <c r="J162" t="n">
+        <v>-1094324.547429828</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-1093999.463060109</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M162" t="n">
+        <v>5.853529974728048e-25</v>
+      </c>
+      <c r="N162" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi090_M</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" t="n">
+        <v>90</v>
+      </c>
+      <c r="G163" t="n">
+        <v>10</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>5</v>
+      </c>
+      <c r="J163" t="n">
+        <v>-1105123.048156039</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-1104426.111072193</v>
+      </c>
+      <c r="L163" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M163" t="n">
+        <v>7.615054945500641e-25</v>
+      </c>
+      <c r="N163" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi120</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>120</v>
+      </c>
+      <c r="G164" t="n">
+        <v>10</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>-1420589.926419724</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-1412705.179068522</v>
+      </c>
+      <c r="L164" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M164" t="n">
+        <v>6.130673009551566e-25</v>
+      </c>
+      <c r="N164" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi120_M</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>120</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>5</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-1431663.986542986</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-1431663.986554198</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M165" t="n">
+        <v>5.764030244067831e-25</v>
+      </c>
+      <c r="N165" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi150</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>150</v>
+      </c>
+      <c r="G166" t="n">
+        <v>10</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>5</v>
+      </c>
+      <c r="J166" t="n">
+        <v>-1695321.956901297</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-1690325.721810431</v>
+      </c>
+      <c r="L166" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M166" t="n">
+        <v>5.942732638021689e-25</v>
+      </c>
+      <c r="N166" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>E4_C_iso_phi150_M</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>150</v>
+      </c>
+      <c r="G167" t="n">
+        <v>10</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>96x96</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>5</v>
+      </c>
+      <c r="J167" t="n">
+        <v>-1710280.58007671</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-1705812.154104328</v>
+      </c>
+      <c r="L167" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M167" t="n">
+        <v>5.983625351750571e-25</v>
+      </c>
+      <c r="N167" t="n">
+        <v>6.337471067996692e-09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>F_tw0.3_circ</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>10</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>5</v>
+      </c>
+      <c r="J168" t="n">
+        <v>-899040.3511199263</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-899040.2689875197</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M168" t="n">
+        <v>7.001362487343579e-25</v>
+      </c>
+      <c r="N168" t="n">
+        <v>7.267588090636986e-09</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>F_tw0.3_ell_phi090</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>90</v>
+      </c>
+      <c r="G169" t="n">
+        <v>10</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>5</v>
+      </c>
+      <c r="J169" t="n">
+        <v>-977936.3031397222</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-977761.2990852288</v>
+      </c>
+      <c r="L169" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M169" t="n">
+        <v>8.567387374472107e-25</v>
+      </c>
+      <c r="N169" t="n">
+        <v>7.267588090636986e-09</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>F_tw0.3_ell_phi150</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" t="n">
+        <v>150</v>
+      </c>
+      <c r="G170" t="n">
+        <v>10</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>5</v>
+      </c>
+      <c r="J170" t="n">
+        <v>-1255159.36671212</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-1242762.324795061</v>
+      </c>
+      <c r="L170" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M170" t="n">
+        <v>7.753581633560335e-25</v>
+      </c>
+      <c r="N170" t="n">
+        <v>7.267588090636986e-09</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>F_tw0.6_circ</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>10</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>5</v>
+      </c>
+      <c r="J171" t="n">
+        <v>-856983.2352498674</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-856952.543009626</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M171" t="n">
+        <v>7.001362487343579e-25</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1.501920806817458e-08</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>F_tw0.6_ell_phi090</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" t="n">
+        <v>90</v>
+      </c>
+      <c r="G172" t="n">
+        <v>10</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>5</v>
+      </c>
+      <c r="J172" t="n">
+        <v>-948791.5296712716</v>
+      </c>
+      <c r="K172" t="n">
+        <v>-948027.5587036546</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M172" t="n">
+        <v>8.567387374472107e-25</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1.501920806817458e-08</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>F_tw0.6_ell_phi150</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" t="n">
+        <v>150</v>
+      </c>
+      <c r="G173" t="n">
+        <v>10</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>5</v>
+      </c>
+      <c r="J173" t="n">
+        <v>-1253536.4244813</v>
+      </c>
+      <c r="K173" t="n">
+        <v>-1241195.863727053</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M173" t="n">
+        <v>7.753581633560335e-25</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1.501920806817458e-08</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>F_tw2.4_circ</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>10</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>5</v>
+      </c>
+      <c r="J174" t="n">
+        <v>-857929.4406721654</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-857712.0050774449</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M174" t="n">
+        <v>7.001362487343579e-25</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0.3196191972977383</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>F_tw2.4_ell_phi090</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" t="n">
+        <v>90</v>
+      </c>
+      <c r="G175" t="n">
+        <v>10</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>5</v>
+      </c>
+      <c r="J175" t="n">
+        <v>-988606.6846172039</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-983550.602187245</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M175" t="n">
+        <v>8.567387374472107e-25</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.3196191972977383</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>F_tw2.4_ell_phi150</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>FOURIER</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>150</v>
+      </c>
+      <c r="G176" t="n">
+        <v>10</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>96x48</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>5</v>
+      </c>
+      <c r="J176" t="n">
         <v>-1364904.493419555</v>
       </c>
-      <c r="K151" t="n">
+      <c r="K176" t="n">
         <v>-1353653.891623355</v>
       </c>
-      <c r="L151" t="n">
+      <c r="L176" t="n">
         <v>2.62</v>
       </c>
-      <c r="M151" t="n">
+      <c r="M176" t="n">
         <v>7.753581633560335e-25</v>
       </c>
-      <c r="N151" t="n">
+      <c r="N176" t="n">
         <v>0.3196191972977383</v>
       </c>
     </row>

--- a/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
+++ b/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhiSweep_ellipse" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convergence_6phi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_lambda_eps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_runs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Verification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PhiSweep_ellipse" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Convergence_6phi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="D_lambda_eps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ablations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Parameters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Production_runs" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
+++ b/PAPER_PROJECT/13_Manuscript/SUPPLEMENTARY_TABLES.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Verification" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PhiSweep_ellipse" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Convergence_6phi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="D_lambda_eps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ablations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Parameters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Production_runs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhiSweep_ellipse" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convergence_6phi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_lambda_eps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_runs" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
